--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536127_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536127_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Á. MERLO</t>
+          <t>A. MERLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2226</v>
+        <v>1.2571</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2226</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.3856</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2226</v>
+        <v>-0.5581</v>
       </c>
       <c r="H6" t="n">
-        <v>0.615</v>
+        <v>-0.3428</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6075</v>
+        <v>-0.2152</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2226</v>
+        <v>1.3346</v>
       </c>
       <c r="K6" t="n">
-        <v>0.615</v>
+        <v>0.4841</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6075</v>
+        <v>0.8505</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.8927</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8269</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.0658</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1699</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1448</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.2553</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.5118</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.7435</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3075</v>
+        <v>-0.0284</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3075</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.7241</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3075</v>
+        <v>-0.4846</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3075</v>
+        <v>0.0598</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.5444</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3075</v>
+        <v>-0.619</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3075</v>
+        <v>0.0615</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6805</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.1344</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.0017</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.1361</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7799</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.7799</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.0451</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.1335</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0883</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MERLO</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0346</v>
+        <v>-1.3717</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.351</v>
+        <v>-0.6561</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3856</v>
+        <v>-0.7156</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7806</v>
+        <v>-1.6771</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9579</v>
+        <v>-0.3599</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8228</v>
+        <v>-1.3172</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1121</v>
+        <v>0.2912</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1309</v>
+        <v>1.6282</v>
       </c>
       <c r="L9" t="n">
-        <v>0.243</v>
+        <v>-1.337</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8927</v>
+        <v>-1.9684</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8269</v>
+        <v>-1.9881</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0658</v>
+        <v>0.0198</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1699</v>
+        <v>-3.1198</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9749</v>
+        <v>-4.8746</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1448</v>
+        <v>1.7549</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2553</v>
+        <v>0.9851</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5118</v>
+        <v>0.2671</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7435</v>
+        <v>0.7179</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.61</v>
+        <v>2.4401</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.6602</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.61</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MONES RIERA</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0284</v>
+        <v>-2.0317</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.6829</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7241</v>
+        <v>-1.3488</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4846</v>
+        <v>-0.7541</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0598</v>
+        <v>-0.0689</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5444</v>
+        <v>-0.6852</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.619</v>
+        <v>0.1215</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6805</v>
+        <v>0.1215</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1344</v>
+        <v>-0.8756</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0017</v>
+        <v>-0.0689</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1361</v>
+        <v>-0.8067</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7799</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7799</v>
+        <v>0.585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0451</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1335</v>
+        <v>-0.0746</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0883</v>
+        <v>0.1619</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,64 +1305,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3717</v>
+        <v>-2.1819</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6561</v>
+        <v>-0.4494</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7156</v>
+        <v>-1.7324</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6771</v>
+        <v>-3.8207</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3599</v>
+        <v>-3.8645</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3172</v>
+        <v>0.0438</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2912</v>
+        <v>-1.9065</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6282</v>
+        <v>-1.947</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.337</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9684</v>
+        <v>-1.9142</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9881</v>
+        <v>-1.9175</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0198</v>
+        <v>0.0033</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1198</v>
+        <v>1.3649</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.8746</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7549</v>
+        <v>1.3649</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9851</v>
+        <v>0.2739</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2671</v>
+        <v>0.237</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7179</v>
+        <v>0.0369</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4401</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6602</v>
+        <v>1.2201</v>
       </c>
       <c r="X11" t="n">
         <v>-1.2201</v>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0317</v>
+        <v>-3.4539</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6829</v>
+        <v>-1.9613</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3488</v>
+        <v>-1.4926</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7541</v>
+        <v>-0.8138</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0689</v>
+        <v>-1.5381</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6852</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1215</v>
+        <v>0.0081</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.0324</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1215</v>
+        <v>0.0405</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8756</v>
+        <v>-0.8219</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0689</v>
+        <v>-1.5057</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8067</v>
+        <v>0.6838</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3649</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R12" t="n">
-        <v>0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="S12" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.3615</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0746</v>
+        <v>-0.0196</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1619</v>
+        <v>-0.3419</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.4986</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2201</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,150 +1471,146 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1819</v>
+        <v>7.014400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4494</v>
+        <v>9.541599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7324</v>
+        <v>-2.5271</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.8207</v>
+        <v>-1.680400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.8645</v>
+        <v>-5.099500000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0438</v>
+        <v>3.4192</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9065</v>
+        <v>11.8926</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.947</v>
+        <v>6.563800000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0405</v>
+        <v>5.3287</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9142</v>
+        <v>-13.5731</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9175</v>
+        <v>-11.6633</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0033</v>
+        <v>-1.9096</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3649</v>
+        <v>0.9748999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-15.5988</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3649</v>
+        <v>16.5738</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2739</v>
+        <v>6.3274</v>
       </c>
       <c r="T13" t="n">
-        <v>0.237</v>
+        <v>3.1417</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0369</v>
+        <v>3.185300000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.3928</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2201</v>
+        <v>10.1061</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536127_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-8.7133</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IREN BCBADAJOZ</t>
+          <t>JAEN PARAISO INTERIOR FS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.7614</v>
+        <v>2.9408</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2688</v>
+        <v>3.0977</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4926</v>
+        <v>-0.1568</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1213</v>
+        <v>2.3945</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8457</v>
+        <v>1.139</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7243000000000001</v>
+        <v>1.2555</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2994</v>
+        <v>2.8752</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3399</v>
+        <v>1.6196</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>1.2555</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8219</v>
+        <v>-0.4807</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5057</v>
+        <v>-0.4807</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6838</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7799</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1699</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3615</v>
+        <v>0.5463</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0196</v>
+        <v>0.2225</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3419</v>
+        <v>0.3239</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4986</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4986</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1625,86 +1621,90 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IREN BCBADAJOZ</t>
+          <t>JAEN PARAISO INTERIOR FS</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.014499999999998</v>
+        <v>2.8815</v>
       </c>
       <c r="E15" t="n">
-        <v>9.541699999999999</v>
+        <v>2.1897</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5271</v>
+        <v>0.6918</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.680300000000001</v>
+        <v>1.7806</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.0997</v>
+        <v>0.5689</v>
       </c>
       <c r="I15" t="n">
-        <v>3.419100000000002</v>
+        <v>1.2118</v>
       </c>
       <c r="J15" t="n">
-        <v>11.8927</v>
+        <v>2.6581</v>
       </c>
       <c r="K15" t="n">
-        <v>6.5638</v>
+        <v>0.7791</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3287</v>
+        <v>1.8791</v>
       </c>
       <c r="M15" t="n">
-        <v>-13.5731</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.6633</v>
+        <v>-0.2102</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9096</v>
+        <v>-0.6673</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9749000000000008</v>
+        <v>1.1699</v>
       </c>
       <c r="Q15" t="n">
-        <v>-15.5988</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>16.5738</v>
+        <v>1.1699</v>
       </c>
       <c r="S15" t="n">
-        <v>6.3274</v>
+        <v>-0.4534</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1417</v>
+        <v>-0.4684</v>
       </c>
       <c r="U15" t="n">
-        <v>3.1853</v>
+        <v>0.015</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3928</v>
+        <v>0.3844</v>
       </c>
       <c r="W15" t="n">
-        <v>10.1061</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.7133</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+        <v>0.3844</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2536127_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9408</v>
+        <v>2.7298</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0977</v>
+        <v>2.7952</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1568</v>
+        <v>-0.0654</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3945</v>
+        <v>0.619</v>
       </c>
       <c r="H16" t="n">
-        <v>1.139</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2555</v>
+        <v>-0.1003</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8752</v>
+        <v>2.4628</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6196</v>
+        <v>2.3008</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2555</v>
+        <v>0.162</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4807</v>
+        <v>-1.8439</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4807</v>
+        <v>-1.5815</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.2623</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.9749</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.9499</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5463</v>
+        <v>0.2473</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2225</v>
+        <v>0.1402</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3239</v>
+        <v>0.1072</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1671</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7298</v>
+        <v>1.799</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7952</v>
+        <v>3.0428</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0654</v>
+        <v>-1.2438</v>
       </c>
       <c r="G17" t="n">
-        <v>0.619</v>
+        <v>1.2252</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1003</v>
+        <v>0.3174</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4628</v>
+        <v>2.5882</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3008</v>
+        <v>2.0052</v>
       </c>
       <c r="L17" t="n">
-        <v>0.162</v>
+        <v>0.583</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8439</v>
+        <v>-1.363</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5815</v>
+        <v>-1.0974</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2623</v>
+        <v>-0.2656</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9749</v>
+        <v>0.195</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9499</v>
+        <v>1.1699</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2473</v>
+        <v>0.3789</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1402</v>
+        <v>0.2095</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1072</v>
+        <v>0.1694</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8885999999999999</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1671</v>
+        <v>1.2201</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.799</v>
+        <v>0.2223</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0428</v>
+        <v>0.9046</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2438</v>
+        <v>-0.6824</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2252</v>
+        <v>-1.5112</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9078000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3174</v>
+        <v>-0.8312</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5882</v>
+        <v>0.0536</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0052</v>
+        <v>0.078</v>
       </c>
       <c r="L18" t="n">
-        <v>0.583</v>
+        <v>-0.0245</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.363</v>
+        <v>-1.5648</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0974</v>
+        <v>-0.758</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2656</v>
+        <v>-0.8067</v>
       </c>
       <c r="P18" t="n">
-        <v>0.195</v>
+        <v>1.5599</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1699</v>
+        <v>1.5599</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3789</v>
+        <v>-1.1523</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2095</v>
+        <v>-0.369</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1694</v>
+        <v>-0.7833</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.3259</v>
       </c>
       <c r="W18" t="n">
         <v>1.2201</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2201</v>
+        <v>0.1058</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6665</v>
+        <v>-0.7105</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9747</v>
+        <v>-1.5534</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6918</v>
+        <v>0.8429</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5656</v>
+        <v>-2.1774</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5689</v>
+        <v>0.3987</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0033</v>
+        <v>-2.5761</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4431</v>
+        <v>-1.0258</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7791</v>
+        <v>0.8862</v>
       </c>
       <c r="L19" t="n">
-        <v>0.664</v>
+        <v>-1.912</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-1.1516</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2102</v>
+        <v>-0.4875</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6673</v>
+        <v>-0.664</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1699</v>
+        <v>1.3649</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1699</v>
+        <v>2.3398</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4534</v>
+        <v>-1.3437</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4684</v>
+        <v>-0.9983</v>
       </c>
       <c r="U19" t="n">
-        <v>0.015</v>
+        <v>-0.3453</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3844</v>
+        <v>1.4457</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.4457</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3844</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.215</v>
+        <v>-0.839</v>
       </c>
       <c r="E20" t="n">
-        <v>1.215</v>
+        <v>0.2338</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-1.0728</v>
       </c>
       <c r="G20" t="n">
-        <v>1.215</v>
+        <v>-0.9478</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.8263</v>
       </c>
       <c r="I20" t="n">
-        <v>1.215</v>
+        <v>-1.7741</v>
       </c>
       <c r="J20" t="n">
-        <v>1.215</v>
+        <v>0.2776</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.5171</v>
       </c>
       <c r="L20" t="n">
-        <v>1.215</v>
+        <v>-1.2395</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-1.2254</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.6908</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.5345</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5599</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.1112</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.1873</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.8301</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2223</v>
+        <v>-2.7816</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9046</v>
+        <v>-1.23</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6824</v>
+        <v>-1.5515</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5112</v>
+        <v>-1.2804</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.68</v>
+        <v>0.1475</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8312</v>
+        <v>-1.4279</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0536</v>
+        <v>-0.9475</v>
       </c>
       <c r="K21" t="n">
-        <v>0.078</v>
+        <v>0.082</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0245</v>
+        <v>-1.0295</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5648</v>
+        <v>-0.333</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.758</v>
+        <v>0.0655</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8067</v>
+        <v>-0.3984</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5599</v>
+        <v>0.9749</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5599</v>
+        <v>0.9749</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1523</v>
+        <v>-0.036</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.369</v>
+        <v>-0.2826</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7833</v>
+        <v>0.2466</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3259</v>
+        <v>-2.4401</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1058</v>
+        <v>-2.4401</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7105</v>
+        <v>-3.2319</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5534</v>
+        <v>-2.2356</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8429</v>
+        <v>-0.9962</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1774</v>
+        <v>1.7021</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3987</v>
+        <v>1.1577</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5761</v>
+        <v>0.5444</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0258</v>
+        <v>2.6487</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8862</v>
+        <v>1.3042</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.912</v>
+        <v>1.3446</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1516</v>
+        <v>-0.9466</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4875</v>
+        <v>-0.1464</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.664</v>
+        <v>-0.8001</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3649</v>
+        <v>-3.8997</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9749</v>
+        <v>-5.8496</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3398</v>
+        <v>1.9499</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3437</v>
+        <v>-1.6443</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9983</v>
+        <v>-0.8649</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3453</v>
+        <v>-0.7794</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4457</v>
+        <v>0.61</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4457</v>
+        <v>1.8301</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.839</v>
+        <v>-3.4899</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2338</v>
+        <v>-0.2602</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0728</v>
+        <v>-3.2297</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9478</v>
+        <v>-0.3002</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8263</v>
+        <v>-0.2517</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7741</v>
+        <v>-0.0485</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2776</v>
+        <v>0.7252</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5171</v>
+        <v>0.6441</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2395</v>
+        <v>0.081</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2254</v>
+        <v>-1.0254</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6908</v>
+        <v>-0.8959</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5345</v>
+        <v>-0.1295</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.39</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5599</v>
+        <v>0.9749</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1112</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.076</v>
+        <v>-0.0104</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1873</v>
+        <v>-0.7392</v>
       </c>
       <c r="V23" t="n">
-        <v>0.61</v>
+        <v>-2.4401</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8301</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2201</v>
+        <v>-2.4401</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7816</v>
+        <v>-5.5603</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.23</v>
+        <v>-4.4576</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5515</v>
+        <v>-1.1028</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2804</v>
+        <v>0.1761</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1475</v>
+        <v>0.1663</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4279</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9475</v>
+        <v>1.2571</v>
       </c>
       <c r="K24" t="n">
-        <v>0.082</v>
+        <v>0.4471</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.0295</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.333</v>
+        <v>-1.081</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0655</v>
+        <v>-0.2808</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3984</v>
+        <v>-0.8001</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9749</v>
+        <v>-2.9248</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-4.8746</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9749</v>
+        <v>1.9499</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.036</v>
+        <v>-1.0345</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2826</v>
+        <v>-0.84</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2466</v>
+        <v>-0.1945</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.4401</v>
+        <v>-1.7772</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4401</v>
+        <v>-1.7772</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,318 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2319</v>
+        <v>-6.0398</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2356</v>
+        <v>2.526999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9962</v>
+        <v>-8.566699999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7021</v>
+        <v>1.680499999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1577</v>
+        <v>5.0998</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5444</v>
+        <v>-3.4191</v>
       </c>
       <c r="J25" t="n">
-        <v>2.6487</v>
+        <v>13.5732</v>
       </c>
       <c r="K25" t="n">
-        <v>1.3042</v>
+        <v>11.6634</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3446</v>
+        <v>1.9097</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9466</v>
+        <v>-11.8929</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1464</v>
+        <v>-6.5637</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8001</v>
+        <v>-5.3285</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.8997</v>
+        <v>-0.9749999999999992</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.8496</v>
+        <v>-16.5737</v>
       </c>
       <c r="R25" t="n">
-        <v>1.9499</v>
+        <v>15.5989</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6443</v>
+        <v>-5.352400000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8649</v>
+        <v>-3.1854</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7794</v>
+        <v>-2.1669</v>
       </c>
       <c r="V25" t="n">
-        <v>0.61</v>
+        <v>-1.3928</v>
       </c>
       <c r="W25" t="n">
-        <v>1.8301</v>
+        <v>8.713200000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536127_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>D. MELERO ZURITA</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>JAEN PARAISO INTERIOR FS</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-3.4899</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.2602</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-3.2297</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.3002</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-0.2517</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-0.0485</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.7252</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.6441</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-1.0254</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-0.8959</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-0.1295</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-0.9749</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.9749</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-0.7495000000000001</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-0.0104</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-0.7392</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-2.4401</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-2.4401</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536127_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A. BADMUS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>JAEN PARAISO INTERIOR FS</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-5.5603</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-4.4576</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-1.1028</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.1761</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1663</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.2571</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.4471</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-1.081</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-0.2808</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-0.8001</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-2.9248</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-4.8746</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.9499</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-1.0345</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="U27" t="n">
-        <v>-0.1945</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-1.7772</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>-1.7772</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>play_by_play_2536127_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>JAEN PARAISO INTERIOR FS</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-6.039799999999999</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.526999999999999</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-8.566700000000001</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.680499999999999</v>
-      </c>
-      <c r="H28" t="n">
-        <v>5.0998</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-3.4192</v>
-      </c>
-      <c r="J28" t="n">
-        <v>13.5732</v>
-      </c>
-      <c r="K28" t="n">
-        <v>11.6634</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.9096</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-11.8929</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-6.5637</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-5.3285</v>
-      </c>
-      <c r="P28" t="n">
-        <v>-0.9750000000000001</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-16.5737</v>
-      </c>
-      <c r="R28" t="n">
-        <v>15.5989</v>
-      </c>
-      <c r="S28" t="n">
-        <v>-5.352399999999999</v>
-      </c>
-      <c r="T28" t="n">
-        <v>-3.1854</v>
-      </c>
-      <c r="U28" t="n">
-        <v>-2.1669</v>
-      </c>
-      <c r="V28" t="n">
-        <v>-1.392800000000001</v>
-      </c>
-      <c r="W28" t="n">
-        <v>8.713200000000001</v>
-      </c>
-      <c r="X28" t="n">
         <v>-10.1061</v>
       </c>
-      <c r="Y28" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
